--- a/media/exports/calibration_register.xlsx
+++ b/media/exports/calibration_register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\users\at-dso-lts-001\documents\calibration_software_full_redesign\labsystem\media\exports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\users\at-dso-lts-001\documents\calibration_software\labsystem\media\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6032D19-68CD-4698-B1D9-286878E9D44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B3828F-F30A-4BC9-B221-8EC518ED42C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2420" yWindow="2420" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="2760" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calibration Register" sheetId="1" r:id="rId1"/>
@@ -1071,5 +1071,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/media/exports/calibration_register.xlsx
+++ b/media/exports/calibration_register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\users\at-dso-lts-001\documents\calibration_software\labsystem\media\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B3828F-F30A-4BC9-B221-8EC518ED42C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC2F2D3-9E63-44D1-86AD-EB9D6BEC88C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="2760" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calibration Register" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>Scope of Work</t>
   </si>
@@ -203,6 +203,30 @@
   </si>
   <si>
     <t>0.5% FS</t>
+  </si>
+  <si>
+    <t>DS-0005</t>
+  </si>
+  <si>
+    <t>AF-116524</t>
+  </si>
+  <si>
+    <t>Deltastar Power Projects LLC</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>DS-0008</t>
+  </si>
+  <si>
+    <t>AF-116527</t>
+  </si>
+  <si>
+    <t>0.00 to 40.00</t>
+  </si>
+  <si>
+    <t>PW00V1</t>
   </si>
 </sst>
 </file>
@@ -582,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1069,6 +1093,166 @@
         <v>55</v>
       </c>
     </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2610004</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2">
+        <v>971573825534</v>
+      </c>
+      <c r="H7" s="2">
+        <v>971483865219</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="3">
+        <v>46303.833333333336</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>46668.833333333336</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T7" s="2">
+        <v>4553</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V7" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="W7" s="2">
+        <v>59.9</v>
+      </c>
+      <c r="X7" s="2">
+        <v>1007.5</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>46303.833333333336</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2610004</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2">
+        <v>971573825534</v>
+      </c>
+      <c r="H8" s="2">
+        <v>971483865219</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="3">
+        <v>46303.833333333336</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>46668.833333333336</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T8" s="2">
+        <v>56643</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V8" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="W8" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="X8" s="2">
+        <v>1007.5</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>46303.833333333336</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
